--- a/Lab2/PhanVungBien.xlsx
+++ b/Lab2/PhanVungBien.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6800" activeTab="5"/>
+    <workbookView windowWidth="18350" windowHeight="6800" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Bai1" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,7 @@
     <sheet name="Bai5" sheetId="5" r:id="rId5"/>
     <sheet name="Bai6" sheetId="6" r:id="rId6"/>
     <sheet name="Bai7" sheetId="7" r:id="rId7"/>
+    <sheet name="Bai8" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="293">
   <si>
     <t>TEST CASE ID:</t>
   </si>
@@ -877,6 +878,9 @@
     <t xml:space="preserve"> Cho đăng nhập lại</t>
   </si>
   <si>
+    <t>TC_06</t>
+  </si>
+  <si>
     <t>Chương trình kiểm tra giá vé xe buýt Hóc môn – Bến xe miền đông</t>
   </si>
   <si>
@@ -983,148 +987,224 @@
     <t>25.5</t>
   </si>
   <si>
-    <t>Test Case ID:</t>
-  </si>
-  <si>
     <t>TC_07</t>
   </si>
   <si>
-    <t>Validate student score analysis file</t>
+    <t>KIỂM THỬ CHƯƠNG TRÌNH SALE CỦA LAZADA</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Giá trị hợp lệ: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[20, 30]</t>
+    </r>
+  </si>
+  <si>
+    <t>Giá trị biên</t>
+  </si>
+  <si>
+    <t>Giá trị ngày</t>
+  </si>
+  <si>
+    <t>Kết quả</t>
+  </si>
+  <si>
+    <t>Dữ liệu nhập : ngày</t>
+  </si>
+  <si>
+    <t>20 – 25</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Coupon giảm </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50%</t>
+    </r>
+  </si>
+  <si>
+    <t>26 – 30</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Coupon giảm </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>70%</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt; 20</t>
+  </si>
+  <si>
+    <t>Lỗi</t>
+  </si>
+  <si>
+    <t>B1max</t>
+  </si>
+  <si>
+    <t>&gt; 30</t>
+  </si>
+  <si>
+    <t>B1max+</t>
+  </si>
+  <si>
+    <t>Không phải số / rỗng</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lỗi</t>
+  </si>
+  <si>
+    <t>6 giá trị</t>
+  </si>
+  <si>
+    <t>19, 20, 25, 26, 30, 31</t>
+  </si>
+  <si>
+    <t>Ngày nhập</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hiển thị lỗi</t>
+  </si>
+  <si>
+    <t>Coupon giảm 50%</t>
+  </si>
+  <si>
+    <t>Coupon giảm 70%</t>
+  </si>
+  <si>
+    <t>Hiển thị lỗi</t>
+  </si>
+  <si>
+    <t>TC_08</t>
+  </si>
+  <si>
+    <t>XÂY DỰNG MẪU KIỂM THỬ FORM LOGIN</t>
   </si>
   <si>
     <t>1.0</t>
   </si>
   <si>
-    <t>S#</t>
-  </si>
-  <si>
-    <t>Prerequisites</t>
-  </si>
-  <si>
-    <t>Test Data Description</t>
-  </si>
-  <si>
-    <t>File input được tải lên hệ thống</t>
-  </si>
-  <si>
-    <t>File hợp lệ (≤100 dòng)</t>
-  </si>
-  <si>
-    <t>File có định dạng đúng</t>
-  </si>
-  <si>
-    <t>File có tên sinh viên &gt;20 ký tự</t>
-  </si>
-  <si>
-    <t>Chương trình phân tích sẵn sàng</t>
-  </si>
-  <si>
-    <t>File có giới tính không hợp lệ</t>
-  </si>
-  <si>
-    <t>File có điểm &lt;0</t>
-  </si>
-  <si>
-    <t>File có điểm &gt;10</t>
-  </si>
-  <si>
-    <t>File có điểm trung bình &lt;5</t>
-  </si>
-  <si>
-    <t>File có điểm trung bình ≥5</t>
-  </si>
-  <si>
-    <t>EQUIVALENCE PARTITIONING</t>
-  </si>
-  <si>
-    <t>Vùng hợp lệ</t>
-  </si>
-  <si>
-    <t>V1</t>
-  </si>
-  <si>
-    <t>Tên ≤ 20 ký tự</t>
-  </si>
-  <si>
-    <t>V2</t>
-  </si>
-  <si>
-    <t>Giới tính: M / F</t>
-  </si>
-  <si>
-    <t>V3</t>
-  </si>
-  <si>
-    <t>Điểm từng môn: 0 – 10</t>
-  </si>
-  <si>
-    <t>V4</t>
-  </si>
-  <si>
-    <t>Số dòng ≤ 100</t>
-  </si>
-  <si>
-    <t>Vùng không hợp lệ</t>
-  </si>
-  <si>
-    <t>Tên &gt; 20 ký tự</t>
-  </si>
-  <si>
-    <t>Giới tính khác M/F</t>
-  </si>
-  <si>
-    <t>Điểm &lt;0 hoặc &gt;10</t>
-  </si>
-  <si>
-    <t>TC ID</t>
-  </si>
-  <si>
-    <t>Test Case Description</t>
-  </si>
-  <si>
-    <t>Input Data</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>File hợp lệ</t>
-  </si>
-  <si>
-    <t>An – M – 6,7,8,5,6</t>
-  </si>
-  <si>
-    <t>Tính điểm TB</t>
-  </si>
-  <si>
-    <t>Điểm TB &lt;5</t>
-  </si>
-  <si>
-    <t>Bình – F – 4,5,3,6,4</t>
-  </si>
-  <si>
-    <t>Không lên lớp</t>
-  </si>
-  <si>
-    <t>Tên quá dài</t>
-  </si>
-  <si>
-    <t>Long…</t>
-  </si>
-  <si>
-    <t>Báo lỗi</t>
-  </si>
-  <si>
-    <t>Sai giới tính</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Điểm &gt;10</t>
-  </si>
-  <si>
-    <t>Điểm âm</t>
+    <r>
+      <t xml:space="preserve">Tên tài khoản: Giá trị hợp lệ: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[3, 30] và Không để trống</t>
+    </r>
+  </si>
+  <si>
+    <t>Mật khẩu: [3, 30] và Không để trống</t>
+  </si>
+  <si>
+    <t>tài khoản</t>
+  </si>
+  <si>
+    <t>&lt;3</t>
+  </si>
+  <si>
+    <t>1 + 1 = 2</t>
+  </si>
+  <si>
+    <t>3-30 ký tự</t>
+  </si>
+  <si>
+    <t>12 − 1 = 11</t>
+  </si>
+  <si>
+    <t>12 + 1 = 13</t>
+  </si>
+  <si>
+    <t>,6 ký tự</t>
+  </si>
+  <si>
+    <t>6 (giữa miền)</t>
+  </si>
+  <si>
+    <t>6-10 ký tự</t>
+  </si>
+  <si>
+    <t>PV8</t>
+  </si>
+  <si>
+    <t>&lt;&gt;10 ký tự</t>
+  </si>
+  <si>
+    <t>5 giá trị biên cho tài khoản</t>
+  </si>
+  <si>
+    <t>0, 2, 3, 30, 31</t>
+  </si>
+  <si>
+    <t>5 giá trị biên cho mật khẩu</t>
+  </si>
+  <si>
+    <t>0, 5, 6, 10, 11</t>
+  </si>
+  <si>
+    <t>Username không được để trống</t>
+  </si>
+  <si>
+    <t>Độ dài Username phải 3–30</t>
+  </si>
+  <si>
+    <t>3 ký tự</t>
+  </si>
+  <si>
+    <t>Độ dài Password phải 6–10</t>
+  </si>
+  <si>
+    <t>Username hoặc Password sai</t>
+  </si>
+  <si>
+    <t>30 ký tự</t>
+  </si>
+  <si>
+    <t>31 ký tự</t>
+  </si>
+  <si>
+    <t>8 ký tự</t>
+  </si>
+  <si>
+    <t>11 ký tự</t>
+  </si>
+  <si>
+    <t>Username đúng</t>
+  </si>
+  <si>
+    <t>Password đúng</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1405,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1335,6 +1415,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1663,7 +1749,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1687,16 +1773,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1705,109 +1791,124 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1815,47 +1916,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2396,26 +2479,26 @@
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="35.6363636363636" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22.4545454545455" style="3" customWidth="1"/>
-    <col min="3" max="3" width="21.2727272727273" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.4545454545455" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27.7272727272727" style="3" customWidth="1"/>
-    <col min="6" max="6" width="24.0909090909091" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.72727272727273" style="3"/>
+    <col min="1" max="1" width="35.6363636363636" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.4545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.2727272727273" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.4545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.7272727272727" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.0909090909091" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2423,13 +2506,13 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -2440,311 +2523,311 @@
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>46028</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="12">
         <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="14"/>
-      <c r="C9" s="23" t="s">
+      <c r="A9" s="4"/>
+      <c r="C9" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="3:7">
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="12">
         <v>99</v>
       </c>
     </row>
     <row r="11" spans="3:7">
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="12">
         <v>100</v>
       </c>
     </row>
     <row r="12" spans="3:7">
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="12">
         <v>101</v>
       </c>
     </row>
     <row r="13" ht="29" spans="3:7">
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="3:4">
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="13" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="12">
         <v>-1</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="12" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="12">
         <v>0</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="12" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="12">
         <v>1</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="12" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="12">
         <v>50</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="12" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="12">
         <v>99</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="12" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="12">
         <v>100</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="12" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="12">
         <v>101</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="12" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="12" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="12" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2758,367 +2841,367 @@
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="35.6363636363636" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22.4545454545455" style="3" customWidth="1"/>
-    <col min="3" max="3" width="21.2727272727273" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.4545454545455" style="3" customWidth="1"/>
-    <col min="5" max="5" width="45.9090909090909" style="3" customWidth="1"/>
-    <col min="6" max="6" width="24.0909090909091" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.72727272727273" style="3"/>
+    <col min="1" max="1" width="35.6363636363636" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.4545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.2727272727273" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.4545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="45.9090909090909" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.0909090909091" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>66</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="14" t="s">
+      <c r="D1" s="1"/>
+      <c r="E1" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>46028</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:7">
-      <c r="A6" s="10" t="s">
+    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="13" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:7">
-      <c r="A7" s="11" t="s">
+    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="A7" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="15" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:7">
-      <c r="A8" s="11" t="s">
+    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="A8" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="15" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:7">
-      <c r="A9" s="14"/>
-      <c r="C9" s="11" t="s">
+    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="A9" s="4"/>
+      <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="15" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" ht="29" spans="3:7">
-      <c r="C10" s="11" t="s">
+    <row r="10" s="1" customFormat="1" ht="29" spans="3:7">
+      <c r="C10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="15" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="16" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" spans="3:7">
-      <c r="C11" s="10" t="s">
+    <row r="11" s="1" customFormat="1" spans="3:7">
+      <c r="C11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="15" t="s">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="16">
         <v>1000</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" ht="29" spans="3:7">
-      <c r="C12" s="14" t="s">
+    <row r="12" s="1" customFormat="1" ht="29" spans="3:7">
+      <c r="C12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="16" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" ht="29" spans="3:7">
-      <c r="C13" s="14" t="s">
+    <row r="13" s="1" customFormat="1" ht="29" spans="3:7">
+      <c r="C13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="14" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14" s="3" customFormat="1" spans="3:4">
-      <c r="C14" s="14" t="s">
+    <row r="14" s="1" customFormat="1" spans="3:4">
+      <c r="C14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" spans="1:1">
-      <c r="A16" s="10" t="s">
+    <row r="16" s="1" customFormat="1" spans="1:1">
+      <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:2">
-      <c r="A17" s="3" t="s">
+    <row r="17" s="1" customFormat="1" spans="1:2">
+      <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:4">
-      <c r="A19" s="17" t="s">
+    <row r="19" s="1" customFormat="1" spans="1:4">
+      <c r="A19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" s="3" customFormat="1" spans="1:4">
-      <c r="A20" s="15" t="s">
+    <row r="20" s="1" customFormat="1" spans="1:4">
+      <c r="A20" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="12">
         <v>0</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="12" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="21" s="3" customFormat="1" spans="1:4">
-      <c r="A21" s="15" t="s">
+    <row r="21" s="1" customFormat="1" spans="1:4">
+      <c r="A21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="12">
         <v>1</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="22" s="3" customFormat="1" spans="1:4">
-      <c r="A22" s="15" t="s">
+    <row r="22" s="1" customFormat="1" spans="1:4">
+      <c r="A22" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="12">
         <v>2</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" s="3" customFormat="1" spans="1:4">
-      <c r="A23" s="15" t="s">
+    <row r="23" s="1" customFormat="1" spans="1:4">
+      <c r="A23" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="12">
         <v>500</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="24" s="3" customFormat="1" spans="1:4">
-      <c r="A24" s="15" t="s">
+    <row r="24" s="1" customFormat="1" spans="1:4">
+      <c r="A24" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="12">
         <v>999</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="25" s="3" customFormat="1" spans="1:4">
-      <c r="A25" s="15" t="s">
+    <row r="25" s="1" customFormat="1" spans="1:4">
+      <c r="A25" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="12">
         <v>1000</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" s="3" customFormat="1" spans="1:4">
-      <c r="A26" s="15" t="s">
+    <row r="26" s="1" customFormat="1" spans="1:4">
+      <c r="A26" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="12">
         <v>1001</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="12" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" s="3" customFormat="1" spans="1:4">
-      <c r="A27" s="15" t="s">
+    <row r="27" s="1" customFormat="1" spans="1:4">
+      <c r="A27" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="12" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" spans="1:4">
-      <c r="A28" s="15" t="s">
+    <row r="28" s="1" customFormat="1" spans="1:4">
+      <c r="A28" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="12" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" spans="1:6">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-    </row>
-    <row r="54" s="3" customFormat="1" spans="1:6">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
+    <row r="29" s="1" customFormat="1" spans="1:6">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:6">
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3132,393 +3215,393 @@
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="41.3636363636364" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30.0909090909091" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.9090909090909" style="3" customWidth="1"/>
-    <col min="4" max="4" width="41.2727272727273" style="3" customWidth="1"/>
-    <col min="5" max="5" width="45.9090909090909" style="3" customWidth="1"/>
-    <col min="6" max="6" width="24.0909090909091" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.72727272727273" style="3"/>
+    <col min="1" max="1" width="41.3636363636364" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.0909090909091" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.9090909090909" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.2727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="45.9090909090909" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.0909090909091" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
+      <c r="D1" s="1"/>
       <c r="E1" s="21" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>46028</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:7">
-      <c r="A6" s="10" t="s">
+    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="13" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:7">
-      <c r="A7" s="11" t="s">
+    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="A7" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="15" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="12" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:7">
-      <c r="A8" s="11" t="s">
+    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="A8" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="15" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="12" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:7">
-      <c r="A9" s="14"/>
-      <c r="C9" s="11" t="s">
+    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="A9" s="4"/>
+      <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="15" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="12" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" spans="3:7">
-      <c r="C10" s="11" t="s">
+    <row r="10" s="1" customFormat="1" spans="3:7">
+      <c r="C10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="15" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" spans="3:7">
-      <c r="C11" s="10" t="s">
+    <row r="11" s="1" customFormat="1" spans="3:7">
+      <c r="C11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="15" t="s">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="12" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" spans="3:7">
-      <c r="C12" s="14" t="s">
+    <row r="12" s="1" customFormat="1" spans="3:7">
+      <c r="C12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="12" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" ht="43.5" spans="3:7">
-      <c r="C13" s="14" t="s">
+    <row r="13" s="1" customFormat="1" ht="43.5" spans="3:7">
+      <c r="C13" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="12" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="14" s="3" customFormat="1" spans="3:4">
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:1">
-      <c r="A16" s="10" t="s">
+    <row r="14" s="1" customFormat="1" spans="3:4">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:1">
+      <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:2">
-      <c r="A17" s="3" t="s">
+    <row r="17" s="1" customFormat="1" spans="1:2">
+      <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:5">
-      <c r="A19" s="17" t="s">
+    <row r="19" s="1" customFormat="1" spans="1:5">
+      <c r="A19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" s="3" customFormat="1" spans="1:5">
-      <c r="A20" s="15" t="s">
+    <row r="20" s="1" customFormat="1" spans="1:5">
+      <c r="A20" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="12" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" s="3" customFormat="1" spans="1:5">
-      <c r="A21" s="15" t="s">
+    <row r="21" s="1" customFormat="1" spans="1:5">
+      <c r="A21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="14" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22" s="3" customFormat="1" spans="1:5">
-      <c r="A22" s="15" t="s">
+    <row r="22" s="1" customFormat="1" spans="1:5">
+      <c r="A22" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="14" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="23" s="3" customFormat="1" spans="1:5">
-      <c r="A23" s="15" t="s">
+    <row r="23" s="1" customFormat="1" spans="1:5">
+      <c r="A23" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="14" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="24" s="3" customFormat="1" spans="1:5">
-      <c r="A24" s="15" t="s">
+    <row r="24" s="1" customFormat="1" spans="1:5">
+      <c r="A24" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="12" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="25" s="3" customFormat="1" spans="1:5">
-      <c r="A25" s="15" t="s">
+    <row r="25" s="1" customFormat="1" spans="1:5">
+      <c r="A25" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="12" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="26" s="3" customFormat="1" spans="1:5">
-      <c r="A26" s="15" t="s">
+    <row r="26" s="1" customFormat="1" spans="1:5">
+      <c r="A26" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="12" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="27" s="3" customFormat="1" spans="1:5">
-      <c r="A27" s="15" t="s">
+    <row r="27" s="1" customFormat="1" spans="1:5">
+      <c r="A27" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="12" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" spans="1:5">
-      <c r="A28" s="15" t="s">
+    <row r="28" s="1" customFormat="1" spans="1:5">
+      <c r="A28" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="12" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" spans="1:6">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-    </row>
-    <row r="54" s="3" customFormat="1" spans="1:6">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
+    <row r="29" s="1" customFormat="1" spans="1:6">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:6">
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3532,375 +3615,375 @@
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="41.3636363636364" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30.0909090909091" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.9090909090909" style="3" customWidth="1"/>
-    <col min="4" max="4" width="41.2727272727273" style="3" customWidth="1"/>
-    <col min="5" max="5" width="45.9090909090909" style="3" customWidth="1"/>
-    <col min="6" max="6" width="24.0909090909091" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.72727272727273" style="3"/>
+    <col min="1" max="1" width="41.3636363636364" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.0909090909091" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.9090909090909" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.2727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="45.9090909090909" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.0909090909091" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>127</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="14" t="s">
+      <c r="D1" s="1"/>
+      <c r="E1" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>46028</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:7">
-      <c r="A6" s="10" t="s">
+    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="13" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:7">
-      <c r="A7" s="14" t="s">
+    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="A7" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="15" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="12" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:7">
-      <c r="A8" s="14" t="s">
+    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="A8" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="15" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:7">
-      <c r="A9" s="14"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="11" t="s">
+    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="15" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" ht="29" spans="3:7">
-      <c r="C10" s="11" t="s">
+    <row r="10" s="1" customFormat="1" ht="29" spans="3:7">
+      <c r="C10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="12" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" spans="3:7">
-      <c r="C11" s="10" t="s">
+    <row r="11" s="1" customFormat="1" spans="3:7">
+      <c r="C11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="13">
         <v>12</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" ht="29" spans="3:7">
-      <c r="C12" s="14" t="s">
+    <row r="12" s="1" customFormat="1" ht="29" spans="3:7">
+      <c r="C12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" ht="29" spans="3:7">
-      <c r="C13" s="14" t="s">
+    <row r="13" s="1" customFormat="1" ht="29" spans="3:7">
+      <c r="C13" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="13" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="14" s="3" customFormat="1" spans="3:4">
-      <c r="C14" s="14" t="s">
+    <row r="14" s="1" customFormat="1" spans="3:4">
+      <c r="C14" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" spans="1:1">
-      <c r="A16" s="10" t="s">
+    <row r="16" s="1" customFormat="1" spans="1:1">
+      <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:2">
-      <c r="A17" s="3" t="s">
+    <row r="17" s="1" customFormat="1" spans="1:2">
+      <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:5">
-      <c r="A19" s="17" t="s">
+    <row r="19" s="1" customFormat="1" spans="1:5">
+      <c r="A19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="17"/>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:5">
-      <c r="A20" s="15" t="s">
+      <c r="E19" s="13"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:5">
+      <c r="A20" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="12">
         <v>0</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="15"/>
-    </row>
-    <row r="21" s="3" customFormat="1" spans="1:5">
-      <c r="A21" s="15" t="s">
+      <c r="E20" s="12"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:5">
+      <c r="A21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="12">
         <v>1</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="E21" s="18"/>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="1:5">
-      <c r="A22" s="15" t="s">
+      <c r="E21" s="14"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:5">
+      <c r="A22" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="12">
         <v>2</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="18"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:5">
-      <c r="A23" s="15" t="s">
+      <c r="E22" s="14"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:5">
+      <c r="A23" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="12">
         <v>6</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="18"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:5">
-      <c r="A24" s="15" t="s">
+      <c r="E23" s="14"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:5">
+      <c r="A24" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="12">
         <v>11</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="15"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="1:5">
-      <c r="A25" s="15" t="s">
+      <c r="E24" s="12"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:5">
+      <c r="A25" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="12">
         <v>12</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="E25" s="15"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:5">
-      <c r="A26" s="15" t="s">
+      <c r="E25" s="12"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:5">
+      <c r="A26" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="12">
         <v>13</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E26" s="15"/>
-    </row>
-    <row r="27" s="3" customFormat="1" spans="1:5">
-      <c r="A27" s="15" t="s">
+      <c r="E26" s="12"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:5">
+      <c r="A27" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E27" s="15"/>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:5">
-      <c r="A28" s="15" t="s">
+      <c r="E27" s="12"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:5">
+      <c r="A28" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E28" s="15"/>
-    </row>
-    <row r="29" s="3" customFormat="1" spans="1:6">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-    </row>
-    <row r="54" s="3" customFormat="1" spans="1:6">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
+      <c r="E28" s="12"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:6">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:6">
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3914,25 +3997,25 @@
   <dimension ref="A1:L54"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="85.0909090909091" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30.0909090909091" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.9090909090909" style="3" customWidth="1"/>
-    <col min="4" max="4" width="41.2727272727273" style="3" customWidth="1"/>
-    <col min="5" max="5" width="55" style="3" customWidth="1"/>
-    <col min="6" max="6" width="24.0909090909091" style="3" customWidth="1"/>
-    <col min="7" max="7" width="8.72727272727273" style="3"/>
-    <col min="8" max="8" width="14.5454545454545" style="3" customWidth="1"/>
-    <col min="9" max="9" width="5.72727272727273" style="3" customWidth="1"/>
-    <col min="10" max="10" width="8.72727272727273" style="3"/>
-    <col min="11" max="11" width="14.5454545454545" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="8.72727272727273" style="3"/>
+    <col min="1" max="1" width="85.0909090909091" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.0909090909091" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.9090909090909" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.2727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="55" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.0909090909091" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.72727272727273" style="1"/>
+    <col min="8" max="8" width="14.5454545454545" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.72727272727273" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.72727272727273" style="1"/>
+    <col min="11" max="11" width="14.5454545454545" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>144</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -3942,53 +4025,53 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>46028</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:11">
-      <c r="A6" s="10" t="s">
+    <row r="6" s="1" customFormat="1" spans="1:11">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="1"/>
       <c r="E6" s="2" t="s">
         <v>146</v>
       </c>
@@ -3999,499 +4082,499 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:12">
-      <c r="A7" s="14" t="s">
+    <row r="7" s="1" customFormat="1" spans="1:12">
+      <c r="A7" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="1"/>
+      <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="13" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:12">
-      <c r="A8" s="14" t="s">
+    <row r="8" s="1" customFormat="1" spans="1:12">
+      <c r="A8" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="11" t="s">
+      <c r="B8" s="1"/>
+      <c r="C8" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="12">
         <v>5</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="12">
         <v>5</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:12">
-      <c r="A9" s="14" t="s">
+    <row r="9" s="1" customFormat="1" spans="1:12">
+      <c r="A9" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="12">
         <v>6</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="12">
         <v>6</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="12">
         <v>6</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" spans="3:12">
-      <c r="C10" s="11" t="s">
+    <row r="10" s="1" customFormat="1" spans="3:12">
+      <c r="C10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="12">
         <v>7</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="12">
         <v>7</v>
       </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="3:12">
-      <c r="C11" s="10" t="s">
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="3:12">
+      <c r="C11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="15" t="s">
+      <c r="D11" s="1"/>
+      <c r="E11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="12">
         <v>19</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="12">
         <v>24</v>
       </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="3:12">
-      <c r="C12" s="14" t="s">
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="3:12">
+      <c r="C12" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="12">
         <v>20</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="12">
         <v>25</v>
       </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-    </row>
-    <row r="13" s="3" customFormat="1" spans="3:12">
-      <c r="C13" s="14" t="s">
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="3:12">
+      <c r="C13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="12">
         <v>21</v>
       </c>
-      <c r="G13" s="17"/>
-      <c r="H13" s="15" t="s">
+      <c r="G13" s="13"/>
+      <c r="H13" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="12">
         <v>26</v>
       </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-    </row>
-    <row r="14" s="3" customFormat="1" spans="3:4">
-      <c r="C14" s="14" t="s">
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="3:4">
+      <c r="C14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="4" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="15" spans="3:3">
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="6" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" spans="3:4">
-      <c r="C16" s="14" t="s">
+    <row r="16" s="1" customFormat="1" spans="3:4">
+      <c r="C16" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" spans="3:4">
-      <c r="C17" s="14" t="s">
+    <row r="17" s="1" customFormat="1" spans="3:4">
+      <c r="C17" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:5">
-      <c r="A19" s="10" t="s">
+    <row r="19" s="1" customFormat="1" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="E19" s="17"/>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B19" s="1"/>
+      <c r="E19" s="13"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:5">
+      <c r="A20" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="E20" s="15"/>
-    </row>
-    <row r="21" s="3" customFormat="1" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="C20" s="1"/>
+      <c r="E20" s="12"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:5">
+      <c r="A21" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="18"/>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="14"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:5">
+      <c r="A22" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E22" s="18"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="5:5">
-      <c r="E23" s="18"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="5:5">
-      <c r="E24" s="15"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="1:5">
-      <c r="A25" s="17" t="s">
+      <c r="E22" s="14"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="5:5">
+      <c r="E23" s="14"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="5:5">
+      <c r="E24" s="12"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:5">
+      <c r="A25" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" s="3" customFormat="1" spans="1:5">
-      <c r="A26" s="15" t="s">
+    <row r="26" s="1" customFormat="1" spans="1:5">
+      <c r="A26" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="12" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" s="3" customFormat="1" spans="1:5">
-      <c r="A27" s="15" t="s">
+    <row r="27" s="1" customFormat="1" spans="1:5">
+      <c r="A27" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="14" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" spans="1:5">
-      <c r="A28" s="15" t="s">
+    <row r="28" s="1" customFormat="1" spans="1:5">
+      <c r="A28" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="14" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" spans="1:6">
-      <c r="A29" s="15" t="s">
+    <row r="29" s="1" customFormat="1" spans="1:6">
+      <c r="A29" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="F29" s="19"/>
+      <c r="F29" s="15"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="12" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="12" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="12" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="14" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="14" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="12" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="12" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="12" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="12" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="54" s="3" customFormat="1" spans="1:6">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
+    <row r="54" s="1" customFormat="1" spans="1:6">
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4505,522 +4588,522 @@
   <dimension ref="A1:L54"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="41.3636363636364" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30.0909090909091" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.9090909090909" style="3" customWidth="1"/>
-    <col min="4" max="4" width="41.2727272727273" style="3" customWidth="1"/>
-    <col min="5" max="5" width="76.8181818181818" style="3" customWidth="1"/>
-    <col min="6" max="6" width="24.0909090909091" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.72727272727273" style="3"/>
+    <col min="1" max="1" width="41.3636363636364" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.0909090909091" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.9090909090909" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.2727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="76.8181818181818" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.0909090909091" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" ht="18" spans="1:5">
+    <row r="1" s="1" customFormat="1" ht="18" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>127</v>
+      <c r="B1" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="9" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="2" s="3" customFormat="1" spans="1:6">
+      <c r="D1" s="1"/>
+      <c r="E1" s="17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>46028</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:3">
-      <c r="A6" s="10" t="s">
+    <row r="6" s="1" customFormat="1" spans="1:3">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" ht="29" spans="1:12">
-      <c r="A7" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="C7" s="10" t="s">
+    <row r="7" s="1" customFormat="1" ht="29" spans="1:12">
+      <c r="A7" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="D7" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="E7" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:12">
-      <c r="A8" s="14" t="s">
+    <row r="8" s="1" customFormat="1" spans="1:12">
+      <c r="A8" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E8" s="15" t="s">
+      <c r="D8" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="E8" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="12">
         <v>0</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="12">
         <v>5</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="12">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:12">
-      <c r="A9" s="14"/>
-      <c r="C9" s="15" t="s">
+    <row r="9" s="1" customFormat="1" spans="1:12">
+      <c r="A9" s="4"/>
+      <c r="C9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="E9" s="16">
+      <c r="D9" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="E9" s="19">
         <v>80000</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="12">
         <v>6</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="12">
         <v>19</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" spans="3:12">
-      <c r="C10" s="15" t="s">
+    <row r="10" s="1" customFormat="1" spans="3:12">
+      <c r="C10" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="D10" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="E10" s="19">
         <v>100000</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="12">
         <v>20</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="12">
         <v>60</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="K10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" spans="3:12">
-      <c r="C11" s="15" t="s">
+    <row r="11" s="1" customFormat="1" spans="3:12">
+      <c r="C11" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="E11" s="16">
+      <c r="D11" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E11" s="19">
         <v>80000</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="12">
         <v>61</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="12">
         <v>120</v>
       </c>
-      <c r="K11" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="L11" s="15">
+      <c r="K11" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="L11" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" spans="3:12">
-      <c r="C12" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="K12" s="15" t="s">
+    <row r="12" s="1" customFormat="1" spans="3:12">
+      <c r="C12" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="L12" s="15">
+      <c r="D12" s="1"/>
+      <c r="K12" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="L12" s="12">
         <v>6</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" spans="3:12">
-      <c r="C13" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="D13" s="14" t="s">
+    <row r="13" s="1" customFormat="1" spans="3:12">
+      <c r="C13" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="K13" s="15" t="s">
+      <c r="D13" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="L13" s="15">
+      <c r="E13" s="1"/>
+      <c r="K13" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="L13" s="12">
         <v>19</v>
       </c>
     </row>
-    <row r="14" s="3" customFormat="1" spans="3:12">
-      <c r="C14" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="D14" s="14" t="s">
+    <row r="14" s="1" customFormat="1" spans="3:12">
+      <c r="C14" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="K14" s="15" t="s">
+      <c r="D14" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="L14" s="15">
+      <c r="E14" s="1"/>
+      <c r="K14" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="L14" s="12">
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="3:12">
-      <c r="C15" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="D15" s="14" t="s">
+      <c r="C15" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="K15" s="15" t="s">
+      <c r="D15" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="L15" s="15">
+      <c r="E15" s="1"/>
+      <c r="K15" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="L15" s="12">
         <v>60</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" spans="11:12">
-      <c r="K16" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="L16" s="15">
+    <row r="16" s="1" customFormat="1" spans="11:12">
+      <c r="K16" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="L16" s="12">
         <v>61</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" spans="11:12">
-      <c r="K17" s="15" t="s">
+    <row r="17" s="1" customFormat="1" spans="11:12">
+      <c r="K17" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L17" s="15">
+      <c r="L17" s="12">
         <v>120</v>
       </c>
     </row>
     <row r="18" spans="11:12">
-      <c r="K18" s="15" t="s">
+      <c r="K18" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="12">
         <v>121</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:1">
-      <c r="A19" s="10" t="s">
+    <row r="19" s="1" customFormat="1" spans="1:1">
+      <c r="A19" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" s="3" customFormat="1" spans="1:2">
-      <c r="A20" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B20" s="14" t="s">
+    <row r="20" s="1" customFormat="1" spans="1:2">
+      <c r="A20" s="1" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="1:5">
-      <c r="A22" s="17" t="s">
+      <c r="B20" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:5">
+      <c r="A22" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="C22" s="17" t="s">
+      <c r="B22" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="E22" s="17"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:5">
-      <c r="A23" s="15" t="s">
+      <c r="D22" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="E22" s="13"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:5">
+      <c r="A23" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="12">
         <v>-1</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="15"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:5">
-      <c r="A24" s="15" t="s">
+      <c r="E23" s="12"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:5">
+      <c r="A24" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="12">
         <v>0</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="E24" s="18"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="1:5">
-      <c r="A25" s="15" t="s">
+      <c r="D24" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E24" s="14"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:5">
+      <c r="A25" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="12">
         <v>1</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="E25" s="18"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:5">
-      <c r="A26" s="15" t="s">
+      <c r="D25" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E25" s="14"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:5">
+      <c r="A26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="12">
         <v>5</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="E26" s="18"/>
-    </row>
-    <row r="27" s="3" customFormat="1" spans="1:5">
-      <c r="A27" s="15" t="s">
+      <c r="D26" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" s="14"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:5">
+      <c r="A27" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="12">
         <v>6</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="19">
         <v>80000</v>
       </c>
-      <c r="E27" s="15"/>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:5">
-      <c r="A28" s="15" t="s">
+      <c r="E27" s="12"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:5">
+      <c r="A28" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="12">
         <v>19</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="19">
         <v>80000</v>
       </c>
-      <c r="E28" s="15"/>
-    </row>
-    <row r="29" s="3" customFormat="1" spans="1:6">
-      <c r="A29" s="15" t="s">
+      <c r="E28" s="12"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:6">
+      <c r="A29" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="12">
         <v>20</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="19">
         <v>100000</v>
       </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="19"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="15"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="12">
         <v>60</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="19">
         <v>100000</v>
       </c>
-      <c r="E30" s="15"/>
+      <c r="E30" s="12"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="12">
         <v>61</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="19">
         <v>80000</v>
       </c>
-      <c r="E31" s="15"/>
+      <c r="E31" s="12"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="12">
         <v>120</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="19">
         <v>80000</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="12">
         <v>121</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="D33" s="15" t="s">
+      <c r="C33" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="B34" s="15" t="s">
+      <c r="A34" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="B34" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="D34" s="15" t="s">
+      <c r="C34" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="B35" s="15" t="s">
+      <c r="A35" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="D35" s="15" t="s">
+      <c r="B35" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D35" s="12" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="54" s="3" customFormat="1" spans="1:6">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
+    <row r="54" s="1" customFormat="1" spans="1:6">
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5031,364 +5114,893 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <dimension ref="A1:K54"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="27.7272727272727" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.4545454545455" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.2727272727273" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.5454545454545" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.4545454545455" style="1" customWidth="1"/>
+    <col min="1" max="1" width="41.3636363636364" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.0909090909091" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.9090909090909" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.2727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="45.9090909090909" style="1" customWidth="1"/>
     <col min="6" max="6" width="24.0909090909091" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.72727272727273" style="1"/>
+    <col min="7" max="7" width="10.7272727272727" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>237</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="1"/>
+      <c r="E1" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>46028</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="29" spans="1:7">
-      <c r="A6" s="5" t="s">
+    <row r="6" s="1" customFormat="1" spans="1:3">
+      <c r="A6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:11">
+      <c r="A7" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="G7" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="J7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:11">
+      <c r="A8" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E8" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:11">
+      <c r="A9" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="12">
+        <v>19</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="3:11">
+      <c r="C10" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="12">
+        <v>20</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="29" spans="3:11">
+      <c r="C11" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="H11" s="12">
+        <v>25</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="3:11">
+      <c r="C12" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="H12" s="12">
+        <v>26</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="29" spans="3:11">
+      <c r="C13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="12">
+        <v>30</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="29" spans="3:11">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="G14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="12">
+        <v>31</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:1">
+      <c r="A16" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:5">
+      <c r="A19" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="13"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:5">
+      <c r="A20" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="12">
+        <v>19</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E20" s="12"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:5">
+      <c r="A21" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="12">
+        <v>20</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E21" s="14"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:5">
+      <c r="A22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="12">
+        <v>25</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E22" s="14"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:5">
+      <c r="A23" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="12">
+        <v>26</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E23" s="14"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:5">
+      <c r="A24" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="12">
+        <v>30</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E24" s="12"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:5">
+      <c r="A25" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="12">
+        <v>31</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" s="12"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:5">
+      <c r="A26" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E26" s="12"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:5">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:5">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:6">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:6">
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K54"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="50.7272727272727" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.4545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.9090909090909" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.2727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="45.9090909090909" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.0909090909091" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7272727272727" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="5">
+        <v>46028</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:3">
+      <c r="A6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:11">
+      <c r="A7" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="G7" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" ht="29" spans="1:7">
-      <c r="A7" s="7">
+      <c r="J7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:11">
+      <c r="A8" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="G8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:11">
+      <c r="A9" s="4"/>
+      <c r="B9" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="G9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="12">
+        <v>19</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="16">
         <v>1</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" ht="29" spans="1:7">
-      <c r="A8" s="7">
-        <v>2</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="D8" s="7">
-        <v>2</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" ht="29" spans="1:7">
-      <c r="A9" s="7">
-        <v>3</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D9" s="7">
-        <v>3</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" spans="4:7">
-      <c r="D10" s="7">
-        <v>4</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="4:7">
-      <c r="D11" s="7">
-        <v>5</v>
-      </c>
-      <c r="E11" s="7" t="s">
+    </row>
+    <row r="10" s="1" customFormat="1" spans="2:11">
+      <c r="B10" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="G10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="12">
+        <v>20</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="29" spans="2:11">
+      <c r="B11" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="G11" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" ht="29" spans="4:7">
-      <c r="D12" s="7">
-        <v>6</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="H11" s="12">
+        <v>25</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="2:11">
+      <c r="B12" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="13" ht="29" spans="4:5">
-      <c r="D13" s="7">
-        <v>7</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="E12" s="12"/>
+      <c r="G12" s="12" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3">
-      <c r="B16" s="1" t="s">
-        <v>255</v>
+      <c r="H12" s="12">
+        <v>26</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="29" spans="2:11">
+      <c r="B13" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="G13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="12">
+        <v>30</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="29" spans="2:11">
+      <c r="B14" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="12">
+        <v>31</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="2:4">
+      <c r="B16" s="11" t="s">
+        <v>147</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3">
-      <c r="B19" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3">
-      <c r="B22" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="B23" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:5">
+      <c r="A19" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="13"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E20" s="12"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="5:5">
+      <c r="E21" s="14"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:5">
+      <c r="A22" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="14"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:5">
+      <c r="A23" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="7" t="s">
+      <c r="B23" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="E23" s="14"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:5">
+      <c r="A24" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="7" t="s">
+      <c r="B24" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="E24" s="12"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:5">
+      <c r="A25" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="7" t="s">
+      <c r="B25" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E25" s="12"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:5">
+      <c r="A26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="7" t="s">
+      <c r="B26" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E26" s="12"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:5">
+      <c r="A27" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="C31" s="7">
-        <v>11</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="7" t="s">
+      <c r="B27" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E27" s="12"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:5">
+      <c r="A28" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B28" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E28" s="12"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:6">
+      <c r="A29" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="C32" s="7">
-        <v>-1</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:6">
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
